--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-09-29 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:04</t>
+    <t xml:space="preserve">2026-09-29 18:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>-0.84</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>61.51</v>
+        <v>61.52</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>62.36</v>
@@ -572,7 +572,7 @@
         <v>47.63</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>51.61</v>
+        <v>51.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:37</t>
+    <t xml:space="preserve">2026-10-05 04:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -569,10 +569,10 @@
         <v>-3.97</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>47.63</v>
+        <v>47.64</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>51.6</v>
+        <v>51.61</v>
       </c>
     </row>
   </sheetData>
